--- a/data/Demand_Excel_Filled.xlsx
+++ b/data/Demand_Excel_Filled.xlsx
@@ -8,21 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaide\PycharmProjects\PythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1ABEE6-20B0-401C-8B1F-F176C40D64B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADC895D-946F-4BB4-9B61-475B7A01AC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Data" sheetId="1" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$1:$E$373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$E$373</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="779">
   <si>
     <t>State</t>
   </si>
@@ -2377,12 +2373,6 @@
   </si>
   <si>
     <t>Cane decor</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
   </si>
 </sst>
 </file>
@@ -2473,7 +2463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2486,10 +2476,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2574,2843 +2560,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jai Devnani" refreshedDate="46169.639771875001" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="372" xr:uid="{4CB2E31A-87C3-4F21-89C1-A77E4F768877}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:E373" sheet="Data"/>
-  </cacheSource>
-  <cacheFields count="5">
-    <cacheField name="State" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Product" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="NIC Code" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="13911" maxValue="47820" count="32">
-        <n v="13911"/>
-        <n v="13912"/>
-        <n v="13913"/>
-        <n v="14103"/>
-        <n v="14109"/>
-        <n v="14202"/>
-        <n v="14301"/>
-        <n v="15122"/>
-        <n v="32120"/>
-        <n v="46305"/>
-        <n v="46306"/>
-        <n v="46411"/>
-        <n v="46412"/>
-        <n v="46413"/>
-        <n v="46419"/>
-        <n v="47190"/>
-        <n v="47211"/>
-        <n v="47214"/>
-        <n v="47215"/>
-        <n v="47219"/>
-        <n v="47510"/>
-        <n v="47531"/>
-        <n v="47532"/>
-        <n v="47592"/>
-        <n v="47711"/>
-        <n v="47713"/>
-        <n v="47722"/>
-        <n v="47732"/>
-        <n v="47733"/>
-        <n v="47734"/>
-        <n v="47735"/>
-        <n v="47820"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Category" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Search Term" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="372">
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Bamboo-cotton blend knit fabric"/>
-    <x v="0"/>
-    <s v="Cotton Knit Fabric Manufacturing"/>
-    <s v="Bamboo cotton"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Cotton jersey single-knit fabric rolls"/>
-    <x v="0"/>
-    <s v="Textile Manufacturing"/>
-    <s v="Cotton fabric"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Acrylic-blend sweater knit fabric"/>
-    <x v="1"/>
-    <s v="Woollen Fabric Manufacturing"/>
-    <s v="Acrylic Sweater"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Woollen rib-knit fabric for winter garments"/>
-    <x v="1"/>
-    <s v="Textile Manufacturing"/>
-    <s v="Wool fabric"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Rayon georgette saree fabric"/>
-    <x v="2"/>
-    <s v="Synthetic Fabric Manufacturing"/>
-    <s v="Georgette Saree"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Polyester chiffon dupatta fabric"/>
-    <x v="2"/>
-    <s v="Synthetic Fabric Manufacturing"/>
-    <s v="Chiffon"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Viscose-modal blend kurta fabric"/>
-    <x v="2"/>
-    <s v="Synthetic Fabric Manufacturing"/>
-    <s v="Kurta Fabric"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Nylon net for lehengas &amp; bridal wear"/>
-    <x v="2"/>
-    <s v="Synthetic Fabric Manufacturing"/>
-    <s v="Nylon net"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Jacquard weave fabric"/>
-    <x v="2"/>
-    <s v="Synthetic Fabric Manufacturing"/>
-    <s v="Jacquard"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Organza &amp; tissue saree fabric"/>
-    <x v="2"/>
-    <s v="Synthetic Fabric Manufacturing"/>
-    <s v="Organza"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Festive pagdis"/>
-    <x v="3"/>
-    <s v="Clothing Accessories Manufacturing"/>
-    <s v="Pagdi"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Patiala turban fabric &amp; pre-tied turbans"/>
-    <x v="3"/>
-    <s v="Clothing Accessories Manufacturing"/>
-    <s v="Turban"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Export T-shirts &amp; polo shirts"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Polo T-shirt + Export Surplus T-shirt"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Sportswear &amp; compression tights"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Sports shorts + Sports tights  + Compression shorts + Compression shorts"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Swimwear &amp; beachwear"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Swimming clothes + Beach clothes"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Denim jeans &amp; jeggings"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Denim Jeans + Jeggings"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Premium linen shirts"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Linen shirt"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Formal trousers &amp; blazers"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Formal Trouser + Formal Pants + Blazer"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Export cotton round-neck T-shirts"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Round neck tshirt"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Polo shirts with 2-button placket"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Polo tshirt"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Dry-fit sportswear &amp; compression gym wear"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Dryfit"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Kids' cotton school uniforms"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="School uniform"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Athleisure jogger-tee co-ord sets"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Jogger set"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Women's cotton nightwear sets"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Cotton Night Suit"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Sublimation-printed graphic tees"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Printed Tshirt"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Bengaluru cut-and-sew garment exports"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Export garments"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Premium co-ord sets for D2C brands"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Co-ord sets + Cord sets"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Activewear sets"/>
-    <x v="4"/>
-    <s v="Apparel Manufacturing"/>
-    <s v="Exercise clothes"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Men's cotton round-neck T-shirts"/>
-    <x v="4"/>
-    <s v="Hosiery &amp; Knitwear Manufacturing"/>
-    <s v="Cotton tshirt"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Thermal innerwear sets"/>
-    <x v="4"/>
-    <s v="Hosiery &amp; Knitwear Manufacturing"/>
-    <s v="Thermal inner"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Sports socks &amp; ankle socks in 6-pack bundles"/>
-    <x v="4"/>
-    <s v="Hosiery &amp; Knitwear Manufacturing"/>
-    <s v="Ankle socks"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Women's leggings &amp; tights"/>
-    <x v="4"/>
-    <s v="Hosiery &amp; Knitwear Manufacturing"/>
-    <s v="Leggings"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Seamless bra packs"/>
-    <x v="4"/>
-    <s v="Hosiery &amp; Knitwear Manufacturing"/>
-    <s v="Bra pack"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Faux fur rugs &amp; decorative throws"/>
-    <x v="5"/>
-    <s v="Textile Products Manufacturing"/>
-    <s v="Rug + Throw"/>
-  </r>
-  <r>
-    <s v="Kashmir"/>
-    <s v="Sheepskin rugs &amp; prayer mats"/>
-    <x v="5"/>
-    <s v="Textile Products Manufacturing"/>
-    <s v="Sajda"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Ludhiana acrylic sweaters — round-neck &amp; V-neck"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Sweater"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Men's woollen half-zip pullovers"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Half zip sweater"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Turtleneck cardigans — women"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Turtleneck"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Kids' school sweaters with zipper"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Kids sweater"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Woollen Patiala caps &amp; beanies"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Woolen beanie"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Matching muffler-glove-cap gift sets"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Muffler + Glove + Winter Cap"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Phulkari-embroidered woollen shawls"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Woolen shawl"/>
-  </r>
-  <r>
-    <s v="Himachal Pradesh"/>
-    <s v="Himachal woollen cap &amp; muffler sets"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Wool cap + Muffler"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Winter woollen shawls"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Woolen Shawl"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Tricity woollen jackets &amp; hoodies"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Woolen Jacket + Hoodie"/>
-  </r>
-  <r>
-    <s v="Ladakh"/>
-    <s v="Yak wool socks &amp; fingerless gloves"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Yak wool"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Pashmina stole &amp; woollen muffler combo sets"/>
-    <x v="6"/>
-    <s v="Woollen Knitwear Manufacturing"/>
-    <s v="Pashmina scarf + Woolen muffler"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Structured leather tote bags"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Leather Tote Bag"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Laptop bags &amp; office backpacks"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Laptop bag + Office backpack"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Handcrafted leather wallets — Diwali gifting"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Wallet"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Crossbody sling bags"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Sling bag"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Leather passport holders &amp; travel pouches"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Passport holder + Travel Pouch"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Genuine leather sandals"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Sandals"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Genuine leather office briefcases"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Leather office bag"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Leather-bound diaries &amp; planners"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Leather diary"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Suede casual loafers"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Loafer"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Leather wallets &amp; belts"/>
-    <x v="7"/>
-    <s v="Leather Goods Manufacturing"/>
-    <s v="Leather Wallet + Leather Belt"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Navratri Bandhani-matched jhumka sets"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Jhumka"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Kundan Meenakari maang tikka"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Maang tikka"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Lac bangle sets"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Lakh chudi"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Temple jewellery sets"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Temple jewellery"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Gold-plated choker necklaces — wedding season"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Gold choker necklace"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Oxidised tribal jewellery from Kutch"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Kalamkari"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Firozabad glass bangle sets"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Glass Bangle"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Kundan polki sets"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Polki set"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Payal / anklets with ghungroo"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Ghungroo"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Silver oxidised earrings with embedded gems"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Silver earrings"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Lac bangle sets"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Lac Bangle"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Tourmaline, garnet &amp; moonstone rings"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Moonstone ring"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Gold-polished Jadau necklace sets"/>
-    <x v="8"/>
-    <s v="Imitation Jewellery Manufacturing"/>
-    <s v="Jadau necklace"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Groundnut oil"/>
-    <x v="9"/>
-    <s v="Wholesale Food &amp; Spices"/>
-    <s v="Groudnut oil"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Sesame seeds &amp; til oil"/>
-    <x v="9"/>
-    <s v="Wholesale Food &amp; Spices"/>
-    <s v="Til tel"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Fenugreek methi"/>
-    <x v="9"/>
-    <s v="Wholesale Food &amp; Spices"/>
-    <s v="Methi"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Jeera &amp; cumin"/>
-    <x v="9"/>
-    <s v="Wholesale Food &amp; Spices"/>
-    <s v="Jeera"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Castor oil"/>
-    <x v="9"/>
-    <s v="Wholesale Food &amp; Spices"/>
-    <s v="Castor oil"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Isabgol / psyllium husk"/>
-    <x v="9"/>
-    <s v="Wholesale Food &amp; Spices"/>
-    <s v="Isabgol"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Darjeeling First Flush tea"/>
-    <x v="10"/>
-    <s v="Tea &amp; Coffee Wholesale"/>
-    <s v="Darjeeling Tea"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Darjeeling Second Flush muscatel tea"/>
-    <x v="10"/>
-    <s v="Tea &amp; Coffee Wholesale"/>
-    <s v="Darjeeling Tea"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Darjeeling white tea"/>
-    <x v="10"/>
-    <s v="Tea &amp; Coffee Wholesale"/>
-    <s v="Darjeeling White tea"/>
-  </r>
-  <r>
-    <s v="Assam"/>
-    <s v="Assam orthodox CTC tea"/>
-    <x v="10"/>
-    <s v="Tea &amp; Coffee Wholesale"/>
-    <s v="Assam tea"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Wholesale cotton fabric — shirting &amp; suiting material"/>
-    <x v="11"/>
-    <s v="Wholesale Trade"/>
-    <s v="Shirt Fabric"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Bulk yarn &amp; knitting thread supply"/>
-    <x v="11"/>
-    <s v="Wholesale Trade"/>
-    <s v="Yarn"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Wholesale monsoon umbrellas &amp; raincoats"/>
-    <x v="12"/>
-    <s v="Wholesale Trade"/>
-    <s v="Umbrella + Raincoat"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Bulk scarves, stoles &amp; neckties"/>
-    <x v="12"/>
-    <s v="Wholesale Trade"/>
-    <s v="Scarf + Tie"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Wholesale PU &amp; leather footwear"/>
-    <x v="13"/>
-    <s v="Wholesale Trade"/>
-    <s v="Leather shoes"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Bulk Kolhapuri chappals &amp; ethnic footwear"/>
-    <x v="13"/>
-    <s v="Wholesale Trade"/>
-    <s v="Kolhapuri Chappal"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Chaniya choli sets"/>
-    <x v="14"/>
-    <s v="Wholesale Clothing"/>
-    <s v="Chaniya Choli"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Bandhani georgette sarees"/>
-    <x v="14"/>
-    <s v="Wholesale Clothing"/>
-    <s v="Bandhani saree"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Wholesale embroidered blouses &amp; dupattas"/>
-    <x v="14"/>
-    <s v="Wholesale Clothing"/>
-    <s v="Embroidery blouse + Embroidered Dupatta"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Zardozi work lehengas"/>
-    <x v="14"/>
-    <s v="Wholesale Clothing"/>
-    <s v="Zardozi lehenga"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Patola silk sarees"/>
-    <x v="14"/>
-    <s v="Wholesale Clothing"/>
-    <s v="Patola Saree"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Jodhpur sheesham wood furniture &amp; side tables"/>
-    <x v="15"/>
-    <s v="Handicrafts &amp; Home Décor"/>
-    <s v="Jodhpur furniture"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Marble Ganesh &amp; Laxmi idols"/>
-    <x v="15"/>
-    <s v="Handicrafts &amp; Home Décor"/>
-    <s v="Marble Idols"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Rajasthani embroidered table runners &amp; napkins — wedding trousseau"/>
-    <x v="15"/>
-    <s v="Handicrafts &amp; Home Décor"/>
-    <s v="Table Runner"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Kalighat painting art prints"/>
-    <x v="15"/>
-    <s v="Gifting &amp; Cultural Retail"/>
-    <s v="Kalighat painting"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Shantiniketan leather bag"/>
-    <x v="15"/>
-    <s v="Gifting &amp; Cultural Retail"/>
-    <s v="Shantiniketan Bag"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Gaming headsets &amp; mechanical keyboards"/>
-    <x v="15"/>
-    <s v="General Retail"/>
-    <s v="Gaming Headset + Mechanical keyboard"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Smart home speakers"/>
-    <x v="15"/>
-    <s v="General Retail"/>
-    <s v="Smart speaker"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Noise-cancelling earbuds"/>
-    <x v="15"/>
-    <s v="General Retail"/>
-    <s v="Noise cancelling earphones"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Ergonomic laptop stands"/>
-    <x v="15"/>
-    <s v="General Retail"/>
-    <s v="Laptop stand"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Air purifier plants in ceramic pots"/>
-    <x v="15"/>
-    <s v="Handicrafts &amp; Home Décor"/>
-    <s v="Plant + Ceramic Pot"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Rose &amp; chocolate Valentine hampers"/>
-    <x v="15"/>
-    <s v="Gifting &amp; Cultural Retail"/>
-    <s v="Valentine Hamper"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Diwali gift sets — dry fruits &amp; silver coin combos"/>
-    <x v="15"/>
-    <s v="Gifting &amp; Cultural Retail"/>
-    <s v="Dry Fruit + Silver Coin"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Holi organic gulal &amp; colour powder sets"/>
-    <x v="15"/>
-    <s v="Gifting &amp; Cultural Retail"/>
-    <s v="Gulal"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Monsoon raincoats &amp; waterproof backpacks"/>
-    <x v="15"/>
-    <s v="General Retail"/>
-    <s v="Raincoat"/>
-  </r>
-  <r>
-    <s v="Dadra &amp; Nagar Haveli and Daman &amp; Diu"/>
-    <s v="Cane &amp; bamboo furniture accessories"/>
-    <x v="15"/>
-    <s v="Handicrafts &amp; Home Décor"/>
-    <s v="Cane furniture + Bamboo furniture"/>
-  </r>
-  <r>
-    <s v="Dadra &amp; Nagar Haveli and Daman &amp; Diu"/>
-    <s v="Handmade terracotta pottery"/>
-    <x v="15"/>
-    <s v="Handicrafts &amp; Home Décor"/>
-    <s v="Terracotta Pottery"/>
-  </r>
-  <r>
-    <s v="Lakshadweep"/>
-    <s v="Coir rope &amp; mat products"/>
-    <x v="15"/>
-    <s v="Handicrafts &amp; Home Décor"/>
-    <s v="Coir rope + Coir mat"/>
-  </r>
-  <r>
-    <s v="Ladakh"/>
-    <s v="Trekking gear essentials"/>
-    <x v="15"/>
-    <s v="General Retail"/>
-    <s v="Trekking gear"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Alphonso mango pulp— summer harvest peak Apr–Jun"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Alphonso Mango"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Alphonso mango ready-to-eat pulp cans"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Alphonso Mango"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Puranpoli mix"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Puranpoli"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Gudi Padwa special mithai hampers"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Shrikhand + Puran Poli"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Malvani masala blends — festive cooking season"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Malvani Masala"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Goda masala"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Goda Masala"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Sol kadhi concentrate"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Sol Kadhi"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Kolhapuri chilli powder"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Chilli Powder"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Nagpur orange gift boxes"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Nagpur Orange"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Chikmagalur single-origin arabica coffee beans"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Arabica coffee"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Coorg robusta filter coffee blend"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Robusta coffee"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Karnataka cardamom chai blend"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Cardamom tea"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Idukki cardamom pods"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Idukki cardamom"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kerala vanilla pods &amp; vanilla extract"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Kerala Vanilla"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kerala cold-pressed coconut oil"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Cold pressed coconut oil"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Nutmeg &amp; mace"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Nutmeg + mace"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kerala Onam spice estate gift box"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Kerala Spices"/>
-  </r>
-  <r>
-    <s v="Himachal Pradesh"/>
-    <s v="Kangra tea gift boxes"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Kangra tea"/>
-  </r>
-  <r>
-    <s v="Goa"/>
-    <s v="Goa cashew nuts &amp; feni"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Goa kaju + feni"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Kashmiri saffron"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Kashmiri saffron"/>
-  </r>
-  <r>
-    <s v="Chandigarh"/>
-    <s v="Gurpurab dry fruit &amp; mithai hampers"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Dry Fruit"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Amritsari papad &amp; pickle gift hampers"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Amritsar Papad"/>
-  </r>
-  <r>
-    <s v="Dadra &amp; Nagar Haveli and Daman &amp; Diu"/>
-    <s v="Kokum sharbat concentrate &amp; spice packets"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Kokum sharbat"/>
-  </r>
-  <r>
-    <s v="Lakshadweep"/>
-    <s v="Coconut jaggery &amp; toddy vinegar"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Coconut jaggery"/>
-  </r>
-  <r>
-    <s v="Puducherry"/>
-    <s v="Pondicherry mango pickle &amp; mor kuzhambu paste"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Mango pickle"/>
-  </r>
-  <r>
-    <s v="Ladakh"/>
-    <s v="Ladakhi dried apricots &amp; apricot jam"/>
-    <x v="16"/>
-    <s v="Food &amp; Grocery Retail"/>
-    <s v="Apricot"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Artisan sourdough bread &amp; croissants"/>
-    <x v="17"/>
-    <s v="Food Retail"/>
-    <s v="Sourdough bread"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Fresh paneer &amp; curd — daily dairy delivery"/>
-    <x v="17"/>
-    <s v="Food Retail"/>
-    <s v="Fresh paneer"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Rajasthani ghewar"/>
-    <x v="18"/>
-    <s v="Sweets &amp; Confectionery Retail"/>
-    <s v="Ghewar"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Besan ladoo &amp; churma"/>
-    <x v="18"/>
-    <s v="Sweets &amp; Confectionery Retail"/>
-    <s v="Besan Ladoo + Churma"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Bikaner namkeen &amp; bhujia"/>
-    <x v="18"/>
-    <s v="Sweets &amp; Confectionery Retail"/>
-    <s v="Bikaner Namkeen"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Mawa kachori &amp; malpua gift boxes"/>
-    <x v="18"/>
-    <s v="Sweets &amp; Confectionery Retail"/>
-    <s v="Mawa kachori + Malpua"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Halwai-style dry fruit barfi sets"/>
-    <x v="18"/>
-    <s v="Sweets &amp; Confectionery Retail"/>
-    <s v="Dry fruit barfi"/>
-  </r>
-  <r>
-    <s v="Goa"/>
-    <s v="Christmas plum cake &amp; Christmas hampers"/>
-    <x v="18"/>
-    <s v="Sweets &amp; Confectionery Retail"/>
-    <s v="Plum cake"/>
-  </r>
-  <r>
-    <s v="Chandigarh"/>
-    <s v="Lohri gajak &amp; rewri gift tins"/>
-    <x v="18"/>
-    <s v="Sweets &amp; Confectionery Retail"/>
-    <s v="Gajak + Rewri"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Whey protein &amp; mass gainer supplements"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Protein + Gainer"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Greek yogurt parfait combos"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Greek Yogurt"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Organic ashwagandha capsules"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Ashwagandha Tablet"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Plant-based protein bars"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Protein Bar"/>
-  </r>
-  <r>
-    <s v="Bihar"/>
-    <s v="Makhana snack packs"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Makhana"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Mathura peda gift boxes"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Mathura Peda"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Petha candy"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Agra Petha"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Organic gurfrom Muzaffarnagar — winter cane harvest"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Jaggery + Gud"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Chyawanprash"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Chyawanprash"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Moringa powder &amp; capsules"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Moringa Powder"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Organic turmeric powder"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Turmeric Powder"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Filter coffee powder"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Filter coffee powder"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Tamarind paste &amp; sambar powder"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Imli chutney +Sambar Powder"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Organic Coorg honey"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Coorg Honey"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Karnataka jackfruit chips &amp; dried mango"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Jackfruit Chips + Dried Mango"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Ragi malt &amp; health mixes"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Ragi Mix"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Multiflora Punjab honey"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Punjab honey"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Makki di atta— winter comfort food"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Makke ka aata"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Organic desi ghee"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Desi ghee"/>
-  </r>
-  <r>
-    <s v="Chandigarh"/>
-    <s v="Pinni— Lohri winter sweet"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Pinni"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Holi gulal powder packs"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Gulal"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Sundarbans honey"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Sundarban Honey"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Patali gur"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Gud"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Bengal Gobindobhog rice"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Gobindobhog rice"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Mishti doimix — winter festive season"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Mishti Doi"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Brahmi &amp; Amla Ayurvedic hair masks"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Amla hair mask"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Triphala churna"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Triphala churna"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Murivenna pain relief oil"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Murivenna oil"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Ashwagandha &amp; Shatavari capsule packs"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Ashwagandha + Shatavari"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Hyderabad haleem-in-a-box"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Hyderabad Haleem"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Nizamabad turmeric"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Nizamabad turmeric"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Sona Masuri rice"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Masuri rice"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Jowar &amp; bajra millet health mix"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Millet snacks"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Kashmiri walnut kernels"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Kashmiri walnut"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Kashmiri dry fruit hampers — badam, akhrot, khumani"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Kashmir dry fruit"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Chyawanprash &amp; immunity kit combos"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Chyawanprash"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Virgin coconut oil"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Virgin coconut oil"/>
-  </r>
-  <r>
-    <s v="Andaman &amp; Nicobar Islands"/>
-    <s v="Andaman coconut products"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Andaman coconut"/>
-  </r>
-  <r>
-    <s v="Andaman &amp; Nicobar Islands"/>
-    <s v="Local honey varieties"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Andaman honey"/>
-  </r>
-  <r>
-    <s v="Ladakh"/>
-    <s v="Ladakh wildflower honey &amp; herbal teas"/>
-    <x v="19"/>
-    <s v="Health Food Retail"/>
-    <s v="Honey + Herbal tea"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Solapuri chaddar"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Solapuri Chaddar"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Kanchipuram silk sarees— Pongal gifting"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Kanchipuram Saree"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Coimbatore cotton Kovai Kora sarees — Pongal new saree tradition"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Pongal Saree"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Madurai cotton sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Madurai Saree"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Karur hand-block print fabric"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Block print fabric"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Handloom cotton sarees with temple border"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Cotton saree"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Pure Mysore silk sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Mysore saree"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Mysore crepe &amp; georgette silk sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Mysore saree"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Ilkal cotton-silk sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Ilkal saree"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Mysore silk dhoti sets"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Silk dhoti"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Bandhani georgette sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Georgette Saree"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Leheriya tie-dye dupattas &amp; sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Leheriya Dupatta"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Kota Doria sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Kota Saree"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Tant cotton fabric by the metre"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Tant cotton"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Kantha-embroidered fabric panels"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Kantha fabric"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Matka silk fabric"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Matka silk"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Pochampally ikat silk sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Pochampally saree"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Gadwal silk sarees with zari"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Gadwal Saree"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Narayanpet silk-cotton sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Narayanpet Saree"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Ikat fabric by the metre"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Ikat fabric"/>
-  </r>
-  <r>
-    <s v="Assam"/>
-    <s v="Muga silk sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Muga saree"/>
-  </r>
-  <r>
-    <s v="Assam"/>
-    <s v="Assam silk gamosa"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Gamosa"/>
-  </r>
-  <r>
-    <s v="Odisha"/>
-    <s v="Orissa ikat handloom sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Ikat saree"/>
-  </r>
-  <r>
-    <s v="Odisha"/>
-    <s v="Sambalpuri ikat sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Sambalpur saree"/>
-  </r>
-  <r>
-    <s v="Madhya Pradesh"/>
-    <s v="Chanderi sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Chanderi saree"/>
-  </r>
-  <r>
-    <s v="Madhya Pradesh"/>
-    <s v="Maheshwari silk-cotton sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Maheshwari silk saree"/>
-  </r>
-  <r>
-    <s v="Andhra Pradesh"/>
-    <s v="Srikalahasti Kalamkari hand-painted sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Kalamkari saree"/>
-  </r>
-  <r>
-    <s v="Andhra Pradesh"/>
-    <s v="Venkatagiri Pattu cotton sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Venkatagiri pattu"/>
-  </r>
-  <r>
-    <s v="Andhra Pradesh"/>
-    <s v="Mangalagiri cotton sarees"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Mangalagiri cotton"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Handwoven phulkari stoles"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Kashmiri Scarf"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Phulkari dupatta sets"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Phulkari Dupatta"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Pashmina shawls"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Pashmina shawl"/>
-  </r>
-  <r>
-    <s v="Ladakh"/>
-    <s v="Ladakhi woollen goncha robe fabric"/>
-    <x v="20"/>
-    <s v="Fabric Retail"/>
-    <s v="Goncha"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Machine-made polyester area rugs"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Rugs"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Tufted rugs with floral/geometric patterns"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Rugs"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Prayer mats — namaz chadar"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Prayer mat"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Jaipur hand-woven wool dhurrie rugs"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Jaipur rugs"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Jaipuri razai quilt"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Jaipur razai"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Alappuzha coir doormat"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Coir doormat"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Woven coir storage baskets"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Coir storage basket"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Natural coir bed mattress"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Coir mattress"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Kashmiri carpet — hand-knotted silk"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Kashmiri carpet"/>
-  </r>
-  <r>
-    <s v="Ladakh"/>
-    <s v="Ladakhi namda&amp; woollen carpets"/>
-    <x v="21"/>
-    <s v="Carpets &amp; Rugs Retail"/>
-    <s v="Woolen carpet"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="3D wallpaper &amp; peel-and-stick wall decals"/>
-    <x v="22"/>
-    <s v="Home Improvement Retail"/>
-    <s v="Stick on wallpaper"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Vinyl flooring &amp; laminate sheets"/>
-    <x v="22"/>
-    <s v="Home Improvement Retail"/>
-    <s v="Vinyl flooring + Laminate sheet"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Solapur terry towel sets"/>
-    <x v="23"/>
-    <s v="Utensils &amp; Home Goods Retail"/>
-    <s v="Towel Set"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Ceramic floor tiles"/>
-    <x v="23"/>
-    <s v="Utensils &amp; Cookware Retail"/>
-    <s v="Ceramic tiles"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Sanitaryware &amp; bathroom fittings"/>
-    <x v="23"/>
-    <s v="Utensils &amp; Cookware Retail"/>
-    <s v="Bathroom fitting"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Diamond-finish cookware sets — Diwali kitchen gifting"/>
-    <x v="23"/>
-    <s v="Utensils &amp; Cookware Retail"/>
-    <s v="Cookware Set"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Aluminium pressure cookers"/>
-    <x v="23"/>
-    <s v="Utensils &amp; Cookware Retail"/>
-    <s v="Pressure cooker"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Steel water bottles"/>
-    <x v="23"/>
-    <s v="Utensils &amp; Home Goods Retail"/>
-    <s v="Steel Water Bottle"/>
-  </r>
-  <r>
-    <s v="Puducherry"/>
-    <s v="Pongal bronze cooking pots &amp; traditional utensils"/>
-    <x v="23"/>
-    <s v="Utensils &amp; Cookware Retail"/>
-    <s v="Bronze utensils"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Oversized graphic tees"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Oversized Tshirt"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Premium co-ord sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Cord set"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Anarkali suits &amp; party-wear lehengas"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Anarkali suit"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Maternity &amp; nursing wear"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Maternity Clothes + Nursing Clothes"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Men's bandhgala kurtas"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Bandhgala + Bandhgala Kurta"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Sequin &amp; mirror-work blouses"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Sequin Clothes"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Diwali special sarees — net &amp; georgette"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Net Sarees + Georgette Sarees"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Garba costume sets — chaniya choli &amp; mojari"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Chaniya Choli + Jutti"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Single-colour Bandhej sarees — Navratri"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Bandhej"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Traditional Gujarati ghagra-choli"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Ghagra Choli"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="White Navratri special kurta sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Navratri Kurta"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Festival edition lehengas"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Lehenga"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Banarasi silk sarees with zari brocade"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Banarasi saree"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Lucknowi chikankari kurta sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Chikankari Kurta"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Chikankari palazzo-suit sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Chikankari"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Zardosi work lehengas &amp; blouses"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Zardozi"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Banarasi brocade dupattas"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Banarasi Dupatta"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Georgette chikankari party-wear tops"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Chikankari"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Banarasi silk shawls"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Banarasi shawl"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Phulkari embroidered dupatta"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Phulkari Dupatta"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Patiala salwar-suit sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Patiala salwar suit"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Amritsari jutti / mojari"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Mojari"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Bridal Phulkari lehenga sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Phulkari lehenga"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Men's kurta-pajama with Phulkari pocket square"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Phulkari kurta"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Rajasthani ghagra-choli sets with mirror work"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Rajasthani Ghagra Choli"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Bandhej sarees &amp; suits"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Bandhej Saree"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Gota patti embroidered lehengas"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Gota lehenga"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Men's Jodhpuri breeches &amp; sherwani sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Jodhpuri Sherwani"/>
-  </r>
-  <r>
-    <s v="Rajasthan"/>
-    <s v="Anarkali suits with Rajasthani block-print"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Anarkali suit"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Tant cotton sarees"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Tant saree"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Baluchari silk sarees"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Baluchari saree"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Jamdani muslin sarees"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Jamdani Saree"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Kantha stitch cotton sarees &amp; dupattas"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Kantha Saree"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Dhuti-panjabi sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Dhoti set"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Dhakai cotton sarees"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Dhakai Saree"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="New collection designer sarees launch"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Designer saree"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kerala kasavu saree"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Kasavu saree"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kerala mundum neriyathum — women's traditional set"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Mundum Neriyathum"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Men's off-white cotton mundu with gold border"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Cotton mundu"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kannur handloom cotton sarees"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Kannur saree"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kasavu-worked cotton dress material"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Kasavu dress"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Vishu special kasavu set"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Vishu set"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Hyderabadi embroidery kurta sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Hyderabad Kurta"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Hyderabadi sherwani with Zardozi"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Hyderabad sherwani"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Men's Hyderabadi kurta-pajama sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Hyderabad Kurta Pajama"/>
-  </r>
-  <r>
-    <s v="Assam"/>
-    <s v="Assam Bihu mekhela chador sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Assam chador"/>
-  </r>
-  <r>
-    <s v="Himachal Pradesh"/>
-    <s v="Kullu shawl"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="kullu shawl"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Kashmiri pashmina shawls"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Pashmina shawl"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Kashmiri kani shawls"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Kani shawl"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Chandni Chowk bridal lehenga"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Bridal Lehenga"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Karol Bagh men's sherwani &amp; Indo-western suit sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Sherwani"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Paharganj block-print cotton kurta sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Kurta Set"/>
-  </r>
-  <r>
-    <s v="Gujarat"/>
-    <s v="Navratri chaniya choli &amp; garba outfits"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Chaniya Choli"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Khadi cotton kurtas"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Khadi Kurta"/>
-  </r>
-  <r>
-    <s v="Chandigarh"/>
-    <s v="Men's premium pathani kurta-pyjama"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Pathani Suit"/>
-  </r>
-  <r>
-    <s v="Chandigarh"/>
-    <s v="Baisakhi embroidered salwar suits"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Embroidery Salwar Suit"/>
-  </r>
-  <r>
-    <s v="Chandigarh"/>
-    <s v="Khadi linen shirts"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Linen shirt"/>
-  </r>
-  <r>
-    <s v="Dadra &amp; Nagar Haveli and Daman &amp; Diu"/>
-    <s v="Warli art print cotton sarees"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Warli Saree"/>
-  </r>
-  <r>
-    <s v="Dadra &amp; Nagar Haveli and Daman &amp; Diu"/>
-    <s v="Cotton casual beachwear &amp; sarongs"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Sarong"/>
-  </r>
-  <r>
-    <s v="Dadra &amp; Nagar Haveli and Daman &amp; Diu"/>
-    <s v="Printed cotton dhoti-kurta sets"/>
-    <x v="24"/>
-    <s v="Clothing Retail"/>
-    <s v="Dhoti set"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="PU leather school shoes"/>
-    <x v="25"/>
-    <s v="Footwear Retail"/>
-    <s v="School shoes"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Chennai leather formal shoes — Ambur/Vellore tanneries"/>
-    <x v="25"/>
-    <s v="Footwear Retail"/>
-    <s v="Formal shoes"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Women's heeled leather sandals"/>
-    <x v="25"/>
-    <s v="Footwear Retail"/>
-    <s v="Leather Sandals"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Punjabi jutti mojaris"/>
-    <x v="25"/>
-    <s v="Footwear Retail"/>
-    <s v="Mojari"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Niacinamide face serums"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Face Serum"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="SPF 50 tinted sunscreen"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Sunscreen SPF 50"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Vitamin C brightening kits"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Vitamin C cream"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Luxury deo gift sets"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Deo"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Waterproof kajal &amp; mascara"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Waterproof Kajal + Waterproof Mascara"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Hair growth oils"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Hair Growth Oil"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Turmeric &amp; neem face packs"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Turmeric face pack + Neem face pack"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Coconut hair oil"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Coconut hair oil"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Natural henna powder"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Henna powder"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Kumkumadi tailam"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Kumkumadi Oil"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Mysore Sandal Soap"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Sandal soap"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Pure sandalwood body lotion"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Chandan lotion"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Vetiver &amp; Neem face wash"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Neem face wash"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Kumkumadi serum"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Kumkumadi Serum"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Brahmi hair oil"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Brahmi Hair Oil"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Mysore sandalwood oil"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Sandalwood Oil"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Virgin coconut oil for hair &amp; skin"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Virgin coconut oil"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Coconut milk shampoo &amp; conditioner"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Coconut milk shampoo"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kera herbal hair oil"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Kera hair oil"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Ayurvedic kumkumadi face serum"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Kumkumadi face serum"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Hyderabad pharma-grade vitamin C supplements"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Vitamin C supplement"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Sunscreen SPF 50 PA++++"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Sunscreen"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Clinical skincare serums"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Skin serum"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Collagen supplements"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Collagen Supplement"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Premium skincare kits"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Skin Care Set"/>
-  </r>
-  <r>
-    <s v="Chandigarh"/>
-    <s v="Teej bangles &amp; red bindi sets"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Red Bindi"/>
-  </r>
-  <r>
-    <s v="Chandigarh"/>
-    <s v="Rose water &amp; almond oil skincare sets"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Rose water + Almond Oil"/>
-  </r>
-  <r>
-    <s v="Puducherry"/>
-    <s v="Pondicherry herbal soaps &amp; organic beauty products"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Herbal soap"/>
-  </r>
-  <r>
-    <s v="Andaman &amp; Nicobar Islands"/>
-    <s v="Organic sea salt &amp; seaweed skin products"/>
-    <x v="26"/>
-    <s v="Beauty &amp; Cosmetics Retail"/>
-    <s v="Seaweed products"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Smart watches &amp; fitness trackers"/>
-    <x v="27"/>
-    <s v="Watches &amp; Clocks Retail"/>
-    <s v="Smart watch"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Luxury wall clocks &amp; table clocks"/>
-    <x v="27"/>
-    <s v="Watches &amp; Clocks Retail"/>
-    <s v="Wall clock + Table clock"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Temple Jewellery of Nagercoil"/>
-    <x v="28"/>
-    <s v="Jewellery Retail"/>
-    <s v="Nagercoil Jewellery"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Silver filigree of Karimnagar"/>
-    <x v="28"/>
-    <s v="Jewellery Retail"/>
-    <s v="Karimnagar Silver"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Silver filigree jewellery"/>
-    <x v="28"/>
-    <s v="Jewellery Retail"/>
-    <s v="Filigree jewellery"/>
-  </r>
-  <r>
-    <s v="Dadra &amp; Nagar Haveli and Daman &amp; Diu"/>
-    <s v="Tribal silver jewellery"/>
-    <x v="28"/>
-    <s v="Jewellery Retail"/>
-    <s v="Tribal Jewellery"/>
-  </r>
-  <r>
-    <s v="Lakshadweep"/>
-    <s v="Coral jewellery"/>
-    <x v="28"/>
-    <s v="Jewellery Retail"/>
-    <s v="Coral jewellery"/>
-  </r>
-  <r>
-    <s v="Andaman &amp; Nicobar Islands"/>
-    <s v="Pearl &amp; shell jewellery"/>
-    <x v="28"/>
-    <s v="Jewellery Retail"/>
-    <s v="Pearl Jewellery + Shell Jewellery"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Indoor plants — money plant &amp; snake plant"/>
-    <x v="29"/>
-    <s v="Plants &amp; Pets Retail"/>
-    <s v="Money plant"/>
-  </r>
-  <r>
-    <s v="Maharashtra"/>
-    <s v="Premium dog food &amp; cat food"/>
-    <x v="29"/>
-    <s v="Plants &amp; Pets Retail"/>
-    <s v="Dog food + Cat food"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Moradabad brass diyas &amp; puja thali sets"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Brass diya + Puja Thali"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Moradabad brassware flower vases &amp; candle stands"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Flower vase + Candle stand"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Agra marble inlay Taj Mahal replicas"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Taj Mahal"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Saharanpur carved wooden photo frames &amp; trays"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Wooden tray + Wooden Photo Frame"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Firozabad glass bangles &amp; decorative items"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Glass Bangle"/>
-  </r>
-  <r>
-    <s v="Uttar Pradesh"/>
-    <s v="Kannauj ittarperfume bottles — Diwali gifting"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Ittar"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Swamimalai bronze icons — Navratri / Diwali ritual gifting"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Bronze Idol"/>
-  </r>
-  <r>
-    <s v="Tamil Nadu"/>
-    <s v="Thanjavur paintings &amp; art plates"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Thanjavur Painting"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Channapatna toys &amp; dolls"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Channapatna Toys"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Mysore agarbathi / incense sticks"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Mysore Agarbatti"/>
-  </r>
-  <r>
-    <s v="Karnataka"/>
-    <s v="Ganjifa cards of Mysore"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Ganjifa"/>
-  </r>
-  <r>
-    <s v="Punjab"/>
-    <s v="Rumala sahib"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Rumal"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Clay Durga idols"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Durga idol"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Terracotta Lakshmi foot-prints — Alpona craft"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Laxmi feet"/>
-  </r>
-  <r>
-    <s v="West Bengal"/>
-    <s v="Bamboo &amp; jute return gift baskets"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Bamboo Basket"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Guruvayur Krishna idol"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Guruvayur idol"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Kathakali mask"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Kathakali Mask"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Onam pookalam kit"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Pookalam flowers"/>
-  </r>
-  <r>
-    <s v="Kerala"/>
-    <s v="Aranmula Kannadi metal mirror"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Aranmula mirror"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Nirmal painted wooden toys"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Wooden Toys"/>
-  </r>
-  <r>
-    <s v="Telangana"/>
-    <s v="Cheriyal scroll painting"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Cheriyal Painting"/>
-  </r>
-  <r>
-    <s v="Himachal Pradesh"/>
-    <s v="Chamba rumal"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Chamba rumal"/>
-  </r>
-  <r>
-    <s v="Bihar"/>
-    <s v="Madhubani paintings"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Madhubani painting"/>
-  </r>
-  <r>
-    <s v="Bihar"/>
-    <s v="Sikki grass craft products"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Sikki grass"/>
-  </r>
-  <r>
-    <s v="Andhra Pradesh"/>
-    <s v="Kondapalli Bommallu wooden toys"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Kondapalli toys"/>
-  </r>
-  <r>
-    <s v="Jammu &amp; Kashmir"/>
-    <s v="Kashmiri papier-mâché handicrafts"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Kashmir handicraft"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Brass diyas &amp; puja thali sets"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Brass Diya + Puja Thali"/>
-  </r>
-  <r>
-    <s v="Dadra &amp; Nagar Haveli and Daman &amp; Diu"/>
-    <s v="Brass diyas"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Brass diya"/>
-  </r>
-  <r>
-    <s v="Lakshadweep"/>
-    <s v="Handwoven pandanus leaf baskets"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Leaf basket"/>
-  </r>
-  <r>
-    <s v="Puducherry"/>
-    <s v="Kolam &amp; rangoli stencil kits"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Rangoli stencil"/>
-  </r>
-  <r>
-    <s v="Andaman &amp; Nicobar Islands"/>
-    <s v="Nicobari cane handicrafts"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Cane decor"/>
-  </r>
-  <r>
-    <s v="Ladakh"/>
-    <s v="Thangka paintings"/>
-    <x v="30"/>
-    <s v="Handicrafts &amp; Religious Articles"/>
-    <s v="Thangka painting"/>
-  </r>
-  <r>
-    <s v="Delhi"/>
-    <s v="Weekly market cotton sarees &amp; dress material"/>
-    <x v="31"/>
-    <s v="Market Stall Retail"/>
-    <s v="Cotton saree"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C84CC8CC-FF68-4657-A95D-150EF1E93409}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:A36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="33">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="33">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5588,189 +2737,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29B0C98-76C5-4789-9B47-DDDA37B377EC}">
-  <dimension ref="A3:A36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>13911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>13912</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>13913</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>14103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>14109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>14202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
-        <v>14301</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
-        <v>15122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
-        <v>32120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
-        <v>46305</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
-        <v>46306</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6">
-        <v>46411</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6">
-        <v>46412</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6">
-        <v>46413</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6">
-        <v>46419</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6">
-        <v>47190</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6">
-        <v>47211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6">
-        <v>47214</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6">
-        <v>47215</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6">
-        <v>47219</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6">
-        <v>47510</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6">
-        <v>47531</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6">
-        <v>47532</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6">
-        <v>47592</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6">
-        <v>47711</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6">
-        <v>47713</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6">
-        <v>47722</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6">
-        <v>47732</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6">
-        <v>47733</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6">
-        <v>47734</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6">
-        <v>47735</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6">
-        <v>47820</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>780</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E373"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
